--- a/KNK업무시스템구축_엑셀/V2/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V2/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
@@ -3846,7 +3846,7 @@
       </c>
       <c r="C5" s="66" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D5" s="67" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="C7" s="66" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D7" s="67" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C9" s="66" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D9" s="67" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="C10" s="75" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D10" s="76" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="C11" s="66" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D11" s="67" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D12" s="76" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="C13" s="66" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D13" s="67" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="C14" s="75" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D14" s="76" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D15" s="67" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C16" s="75" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D16" s="76" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="C17" s="66" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D17" s="67" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="C18" s="75" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D18" s="76" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="C19" s="66" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D19" s="67" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="C20" s="75" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D20" s="76" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D21" s="67" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="C22" s="75" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D22" s="76" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D23" s="67" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C24" s="75" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D24" s="76" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="C25" s="66" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D25" s="67" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="C26" s="75" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D26" s="76" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="C27" s="66" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D27" s="67" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="C30" s="75" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D30" s="76" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="C31" s="66" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D31" s="67" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="C32" s="75" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D32" s="76" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="C33" s="66" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D33" s="67" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="C34" s="75" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D34" s="76" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C35" s="66" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D35" s="67" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="C37" s="66" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D37" s="67" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="C38" s="75" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D38" s="76" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="C39" s="66" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D39" s="67" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="C42" s="75" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D42" s="76" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C43" s="66" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D43" s="67" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="C44" s="75" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D44" s="76" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="C45" s="66" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D45" s="67" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="C46" s="75" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D46" s="76" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="C47" s="66" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D47" s="67" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="C49" s="66" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D49" s="67" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="C50" s="75" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D50" s="76" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="C51" s="66" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D51" s="67" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="C52" s="75" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D52" s="76" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="C53" s="66" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D53" s="67" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="C54" s="75" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D54" s="76" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="C55" s="66" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D55" s="67" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="C56" s="75" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D56" s="76" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="C57" s="66" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D57" s="67" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="C58" s="75" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D58" s="76" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="C59" s="66" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D59" s="67" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="C61" s="66" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D61" s="67" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C62" s="75" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D62" s="76" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="C63" s="66" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D63" s="67" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="C64" s="75" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D64" s="76" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="C66" s="75" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D66" s="76" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C67" s="66" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D67" s="67" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="C68" s="75" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D68" s="76" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="C69" s="66" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D69" s="67" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C70" s="75" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D70" s="76" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="C71" s="66" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D71" s="67" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="C72" s="75" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D72" s="76" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="C73" s="66" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D73" s="67" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C74" s="75" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D74" s="76" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="C76" s="75" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D76" s="76" t="inlineStr">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="C77" s="66" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D77" s="67" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="C78" s="75" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D78" s="76" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="C79" s="66" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D79" s="67" t="inlineStr">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="C80" s="75" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D80" s="76" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="C81" s="66" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D81" s="67" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="C82" s="75" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D82" s="76" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="C83" s="66" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D83" s="67" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="C86" s="75" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D86" s="76" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="C87" s="66" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D87" s="67" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="C88" s="75" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D88" s="76" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="C89" s="66" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D89" s="67" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="C90" s="75" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D90" s="76" t="inlineStr">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="C92" s="75" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D92" s="76" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="C93" s="66" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D93" s="67" t="inlineStr">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="C94" s="75" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D94" s="76" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="C95" s="66" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D95" s="67" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="C96" s="75" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D96" s="76" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="C97" s="66" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D97" s="67" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="C98" s="75" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D98" s="76" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="C99" s="66" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="67" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="C101" s="66" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D101" s="67" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="C102" s="75" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D102" s="76" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="C103" s="66" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D103" s="67" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="C104" s="75" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D104" s="76" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="C105" s="66" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D105" s="67" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="C106" s="75" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D106" s="76" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="C108" s="75" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D108" s="76" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="C110" s="75" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D110" s="76" t="inlineStr">
@@ -15978,7 +15978,7 @@
       </c>
       <c r="C5" s="66" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D5" s="66" t="inlineStr">
@@ -16122,7 +16122,7 @@
       </c>
       <c r="C7" s="66" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D7" s="66" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="C9" s="66" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D9" s="66" t="inlineStr">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="C10" s="75" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D10" s="75" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="C11" s="66" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D11" s="66" t="inlineStr">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D12" s="75" t="inlineStr">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="C13" s="66" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D13" s="66" t="inlineStr">
@@ -16626,7 +16626,7 @@
       </c>
       <c r="C14" s="75" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D14" s="75" t="inlineStr">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D15" s="66" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="C16" s="75" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D16" s="75" t="inlineStr">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="C17" s="66" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D17" s="66" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="C18" s="75" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D18" s="75" t="inlineStr">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="C19" s="66" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D19" s="66" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="C20" s="75" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D20" s="75" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D21" s="66" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="C22" s="75" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D22" s="75" t="inlineStr">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D23" s="66" t="inlineStr">
@@ -17346,7 +17346,7 @@
       </c>
       <c r="C24" s="75" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D24" s="75" t="inlineStr">
@@ -17418,7 +17418,7 @@
       </c>
       <c r="C25" s="66" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D25" s="66" t="inlineStr">
@@ -17490,7 +17490,7 @@
       </c>
       <c r="C26" s="75" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D26" s="75" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="C27" s="66" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D27" s="66" t="inlineStr">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="C30" s="75" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D30" s="75" t="inlineStr">
@@ -17850,7 +17850,7 @@
       </c>
       <c r="C31" s="66" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D31" s="66" t="inlineStr">
@@ -17922,7 +17922,7 @@
       </c>
       <c r="C32" s="75" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D32" s="75" t="inlineStr">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="C33" s="66" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D33" s="66" t="inlineStr">
@@ -18066,7 +18066,7 @@
       </c>
       <c r="C34" s="75" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D34" s="75" t="inlineStr">
@@ -18138,7 +18138,7 @@
       </c>
       <c r="C35" s="66" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D35" s="66" t="inlineStr">
@@ -18282,7 +18282,7 @@
       </c>
       <c r="C37" s="66" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D37" s="66" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C38" s="75" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D38" s="75" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="C39" s="66" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D39" s="66" t="inlineStr">
@@ -18642,7 +18642,7 @@
       </c>
       <c r="C42" s="75" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D42" s="75" t="inlineStr">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="C43" s="66" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D43" s="66" t="inlineStr">
@@ -18786,7 +18786,7 @@
       </c>
       <c r="C44" s="75" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D44" s="75" t="inlineStr">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="C45" s="66" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D45" s="66" t="inlineStr">
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C46" s="75" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D46" s="75" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="C47" s="66" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D47" s="66" t="inlineStr">
@@ -19146,7 +19146,7 @@
       </c>
       <c r="C49" s="66" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D49" s="66" t="inlineStr">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="C50" s="75" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D50" s="75" t="inlineStr">
@@ -19290,7 +19290,7 @@
       </c>
       <c r="C51" s="66" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D51" s="66" t="inlineStr">
@@ -19362,7 +19362,7 @@
       </c>
       <c r="C52" s="75" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D52" s="75" t="inlineStr">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="C53" s="66" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D53" s="66" t="inlineStr">
@@ -19506,7 +19506,7 @@
       </c>
       <c r="C54" s="75" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D54" s="75" t="inlineStr">
@@ -19578,7 +19578,7 @@
       </c>
       <c r="C55" s="66" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D55" s="66" t="inlineStr">
@@ -19650,7 +19650,7 @@
       </c>
       <c r="C56" s="75" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D56" s="75" t="inlineStr">
@@ -19722,7 +19722,7 @@
       </c>
       <c r="C57" s="66" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D57" s="66" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="C58" s="75" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D58" s="75" t="inlineStr">
@@ -19866,7 +19866,7 @@
       </c>
       <c r="C59" s="66" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D59" s="66" t="inlineStr">
@@ -20010,7 +20010,7 @@
       </c>
       <c r="C61" s="66" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D61" s="66" t="inlineStr">
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C62" s="75" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D62" s="75" t="inlineStr">
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C63" s="66" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D63" s="66" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="C64" s="75" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D64" s="75" t="inlineStr">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C66" s="75" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D66" s="75" t="inlineStr">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C67" s="66" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D67" s="66" t="inlineStr">
@@ -20514,7 +20514,7 @@
       </c>
       <c r="C68" s="75" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D68" s="75" t="inlineStr">
@@ -20586,7 +20586,7 @@
       </c>
       <c r="C69" s="66" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D69" s="66" t="inlineStr">
@@ -20658,7 +20658,7 @@
       </c>
       <c r="C70" s="75" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D70" s="75" t="inlineStr">
@@ -20730,7 +20730,7 @@
       </c>
       <c r="C71" s="66" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D71" s="66" t="inlineStr">
@@ -20802,7 +20802,7 @@
       </c>
       <c r="C72" s="75" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D72" s="75" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="C73" s="66" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D73" s="66" t="inlineStr">
@@ -20946,7 +20946,7 @@
       </c>
       <c r="C74" s="75" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D74" s="75" t="inlineStr">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="C76" s="75" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D76" s="75" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="C77" s="66" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D77" s="66" t="inlineStr">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="C78" s="75" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D78" s="75" t="inlineStr">
@@ -21306,7 +21306,7 @@
       </c>
       <c r="C79" s="66" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D79" s="66" t="inlineStr">
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C80" s="75" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D80" s="75" t="inlineStr">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="C81" s="66" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D81" s="66" t="inlineStr">
@@ -21522,7 +21522,7 @@
       </c>
       <c r="C82" s="75" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D82" s="75" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="C83" s="66" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D83" s="66" t="inlineStr">
@@ -21810,7 +21810,7 @@
       </c>
       <c r="C86" s="75" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D86" s="75" t="inlineStr">
@@ -21882,7 +21882,7 @@
       </c>
       <c r="C87" s="66" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D87" s="66" t="inlineStr">
@@ -21954,7 +21954,7 @@
       </c>
       <c r="C88" s="75" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D88" s="75" t="inlineStr">
@@ -22026,7 +22026,7 @@
       </c>
       <c r="C89" s="66" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D89" s="66" t="inlineStr">
@@ -22098,7 +22098,7 @@
       </c>
       <c r="C90" s="75" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D90" s="75" t="inlineStr">
@@ -22242,7 +22242,7 @@
       </c>
       <c r="C92" s="75" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D92" s="75" t="inlineStr">
@@ -22314,7 +22314,7 @@
       </c>
       <c r="C93" s="66" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D93" s="66" t="inlineStr">
@@ -22386,7 +22386,7 @@
       </c>
       <c r="C94" s="75" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D94" s="75" t="inlineStr">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="C95" s="66" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D95" s="66" t="inlineStr">
@@ -22530,7 +22530,7 @@
       </c>
       <c r="C96" s="75" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D96" s="75" t="inlineStr">
@@ -22602,7 +22602,7 @@
       </c>
       <c r="C97" s="66" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D97" s="66" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="C98" s="75" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D98" s="75" t="inlineStr">
@@ -22746,7 +22746,7 @@
       </c>
       <c r="C99" s="66" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="66" t="inlineStr">
@@ -22890,7 +22890,7 @@
       </c>
       <c r="C101" s="66" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D101" s="66" t="inlineStr">
@@ -22962,7 +22962,7 @@
       </c>
       <c r="C102" s="75" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D102" s="75" t="inlineStr">
@@ -23034,7 +23034,7 @@
       </c>
       <c r="C103" s="66" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D103" s="66" t="inlineStr">
@@ -23106,7 +23106,7 @@
       </c>
       <c r="C104" s="75" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D104" s="75" t="inlineStr">
@@ -23178,7 +23178,7 @@
       </c>
       <c r="C105" s="66" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D105" s="66" t="inlineStr">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="C106" s="75" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D106" s="75" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="C108" s="75" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D108" s="75" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="C110" s="75" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D110" s="75" t="inlineStr">
@@ -27211,7 +27211,7 @@
       </c>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>T-260324-2</t>
+          <t>T-260324-1</t>
         </is>
       </c>
       <c r="D12" s="76" t="inlineStr">
@@ -27769,7 +27769,7 @@
       </c>
       <c r="C18" s="75" t="inlineStr">
         <is>
-          <t>T-260324-3</t>
+          <t>T-260324-2</t>
         </is>
       </c>
       <c r="D18" s="76" t="inlineStr">
@@ -27862,7 +27862,7 @@
       </c>
       <c r="C19" s="66" t="inlineStr">
         <is>
-          <t>T-260324-4</t>
+          <t>T-260324-3</t>
         </is>
       </c>
       <c r="D19" s="67" t="inlineStr">
@@ -28048,7 +28048,7 @@
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>T-260326-2</t>
+          <t>T-260326-1</t>
         </is>
       </c>
       <c r="D21" s="67" t="inlineStr">
@@ -28141,7 +28141,7 @@
       </c>
       <c r="C22" s="75" t="inlineStr">
         <is>
-          <t>T-260326-3</t>
+          <t>T-260326-2</t>
         </is>
       </c>
       <c r="D22" s="76" t="inlineStr">
@@ -28234,7 +28234,7 @@
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>T-260326-4</t>
+          <t>T-260326-3</t>
         </is>
       </c>
       <c r="D23" s="67" t="inlineStr">
@@ -28420,7 +28420,7 @@
       </c>
       <c r="C25" s="66" t="inlineStr">
         <is>
-          <t>T-260324-6</t>
+          <t>T-260324-5</t>
         </is>
       </c>
       <c r="D25" s="67" t="inlineStr">
@@ -28513,7 +28513,7 @@
       </c>
       <c r="C26" s="75" t="inlineStr">
         <is>
-          <t>T-260324-7</t>
+          <t>T-260324-6</t>
         </is>
       </c>
       <c r="D26" s="76" t="inlineStr">
@@ -28606,7 +28606,7 @@
       </c>
       <c r="C27" s="66" t="inlineStr">
         <is>
-          <t>T-260401-2</t>
+          <t>T-260401-1</t>
         </is>
       </c>
       <c r="D27" s="67" t="inlineStr">
@@ -28699,7 +28699,7 @@
       </c>
       <c r="C28" s="75" t="inlineStr">
         <is>
-          <t>T-260401-3</t>
+          <t>T-260401-2</t>
         </is>
       </c>
       <c r="D28" s="76" t="inlineStr">
@@ -28978,7 +28978,7 @@
       </c>
       <c r="C31" s="66" t="inlineStr">
         <is>
-          <t>T-260330-2</t>
+          <t>T-260330-1</t>
         </is>
       </c>
       <c r="D31" s="67" t="inlineStr">
@@ -29071,7 +29071,7 @@
       </c>
       <c r="C32" s="75" t="inlineStr">
         <is>
-          <t>T-260330-3</t>
+          <t>T-260330-2</t>
         </is>
       </c>
       <c r="D32" s="76" t="inlineStr">
@@ -29164,7 +29164,7 @@
       </c>
       <c r="C33" s="66" t="inlineStr">
         <is>
-          <t>T-260330-4</t>
+          <t>T-260330-3</t>
         </is>
       </c>
       <c r="D33" s="67" t="inlineStr">
@@ -29350,7 +29350,7 @@
       </c>
       <c r="C35" s="66" t="inlineStr">
         <is>
-          <t>T-260403-2</t>
+          <t>T-260403-1</t>
         </is>
       </c>
       <c r="D35" s="67" t="inlineStr">
@@ -29443,7 +29443,7 @@
       </c>
       <c r="C36" s="75" t="inlineStr">
         <is>
-          <t>T-260403-3</t>
+          <t>T-260403-2</t>
         </is>
       </c>
       <c r="D36" s="76" t="inlineStr">
@@ -29536,7 +29536,7 @@
       </c>
       <c r="C37" s="66" t="inlineStr">
         <is>
-          <t>T-260403-4</t>
+          <t>T-260403-3</t>
         </is>
       </c>
       <c r="D37" s="67" t="inlineStr">
@@ -29629,7 +29629,7 @@
       </c>
       <c r="C38" s="75" t="inlineStr">
         <is>
-          <t>T-260403-5</t>
+          <t>T-260403-4</t>
         </is>
       </c>
       <c r="D38" s="76" t="inlineStr">
@@ -29722,7 +29722,7 @@
       </c>
       <c r="C39" s="66" t="inlineStr">
         <is>
-          <t>T-260312-2</t>
+          <t>T-260312-1</t>
         </is>
       </c>
       <c r="D39" s="67" t="inlineStr">
@@ -29819,7 +29819,7 @@
       </c>
       <c r="C40" s="75" t="inlineStr">
         <is>
-          <t>T-260312-3</t>
+          <t>T-260312-2</t>
         </is>
       </c>
       <c r="D40" s="76" t="inlineStr">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C41" s="66" t="inlineStr">
         <is>
-          <t>T-260312-4</t>
+          <t>T-260312-3</t>
         </is>
       </c>
       <c r="D41" s="67" t="inlineStr">
@@ -30292,7 +30292,7 @@
       </c>
       <c r="C45" s="66" t="inlineStr">
         <is>
-          <t>T-260318-2</t>
+          <t>T-260318-1</t>
         </is>
       </c>
       <c r="D45" s="67" t="inlineStr">
@@ -30385,7 +30385,7 @@
       </c>
       <c r="C46" s="75" t="inlineStr">
         <is>
-          <t>T-260324-11</t>
+          <t>T-260324-10</t>
         </is>
       </c>
       <c r="D46" s="76" t="inlineStr">
@@ -30478,7 +30478,7 @@
       </c>
       <c r="C47" s="66" t="inlineStr">
         <is>
-          <t>T-260325-2</t>
+          <t>T-260325-1</t>
         </is>
       </c>
       <c r="D47" s="67" t="inlineStr">
@@ -30571,7 +30571,7 @@
       </c>
       <c r="C48" s="75" t="inlineStr">
         <is>
-          <t>T-260319-2</t>
+          <t>T-260319-1</t>
         </is>
       </c>
       <c r="D48" s="76" t="inlineStr">
@@ -30664,7 +30664,7 @@
       </c>
       <c r="C49" s="66" t="inlineStr">
         <is>
-          <t>T-260319-3</t>
+          <t>T-260319-2</t>
         </is>
       </c>
       <c r="D49" s="67" t="inlineStr">
@@ -30757,7 +30757,7 @@
       </c>
       <c r="C50" s="75" t="inlineStr">
         <is>
-          <t>T-260325-3</t>
+          <t>T-260325-2</t>
         </is>
       </c>
       <c r="D50" s="76" t="inlineStr">
@@ -30850,7 +30850,7 @@
       </c>
       <c r="C51" s="66" t="inlineStr">
         <is>
-          <t>T-260401-5</t>
+          <t>T-260401-4</t>
         </is>
       </c>
       <c r="D51" s="67" t="inlineStr">
@@ -30943,7 +30943,7 @@
       </c>
       <c r="C52" s="75" t="inlineStr">
         <is>
-          <t>T-260331-4</t>
+          <t>T-260331-3</t>
         </is>
       </c>
       <c r="D52" s="76" t="inlineStr">
@@ -31040,7 +31040,7 @@
       </c>
       <c r="C53" s="66" t="inlineStr">
         <is>
-          <t>T-260331-5</t>
+          <t>T-260331-4</t>
         </is>
       </c>
       <c r="D53" s="67" t="inlineStr">
@@ -31137,7 +31137,7 @@
       </c>
       <c r="C54" s="75" t="inlineStr">
         <is>
-          <t>T-260331-6</t>
+          <t>T-260331-5</t>
         </is>
       </c>
       <c r="D54" s="76" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="C55" s="66" t="inlineStr">
         <is>
-          <t>T-260331-7</t>
+          <t>T-260331-6</t>
         </is>
       </c>
       <c r="D55" s="67" t="inlineStr">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="C56" s="75" t="inlineStr">
         <is>
-          <t>T-260324-12</t>
+          <t>T-260324-11</t>
         </is>
       </c>
       <c r="D56" s="76" t="inlineStr">
@@ -31428,7 +31428,7 @@
       </c>
       <c r="C57" s="66" t="inlineStr">
         <is>
-          <t>T-260313-2</t>
+          <t>T-260313-1</t>
         </is>
       </c>
       <c r="D57" s="67" t="inlineStr">
@@ -31521,7 +31521,7 @@
       </c>
       <c r="C58" s="75" t="inlineStr">
         <is>
-          <t>T-260326-5</t>
+          <t>T-260326-4</t>
         </is>
       </c>
       <c r="D58" s="76" t="inlineStr">
@@ -31715,7 +31715,7 @@
       </c>
       <c r="C60" s="75" t="inlineStr">
         <is>
-          <t>T-260331-8</t>
+          <t>T-260331-7</t>
         </is>
       </c>
       <c r="D60" s="76" t="inlineStr">
@@ -31808,7 +31808,7 @@
       </c>
       <c r="C61" s="66" t="inlineStr">
         <is>
-          <t>T-260331-9</t>
+          <t>T-260331-8</t>
         </is>
       </c>
       <c r="D61" s="67" t="inlineStr">
@@ -31901,7 +31901,7 @@
       </c>
       <c r="C62" s="75" t="inlineStr">
         <is>
-          <t>T-260331-10</t>
+          <t>T-260331-9</t>
         </is>
       </c>
       <c r="D62" s="76" t="inlineStr">
@@ -31994,7 +31994,7 @@
       </c>
       <c r="C63" s="66" t="inlineStr">
         <is>
-          <t>T-260318-3</t>
+          <t>T-260318-2</t>
         </is>
       </c>
       <c r="D63" s="67" t="inlineStr">
@@ -32087,7 +32087,7 @@
       </c>
       <c r="C64" s="75" t="inlineStr">
         <is>
-          <t>T-260325-4</t>
+          <t>T-260325-3</t>
         </is>
       </c>
       <c r="D64" s="76" t="inlineStr">
@@ -32180,7 +32180,7 @@
       </c>
       <c r="C65" s="66" t="inlineStr">
         <is>
-          <t>T-260325-5</t>
+          <t>T-260325-4</t>
         </is>
       </c>
       <c r="D65" s="67" t="inlineStr">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C66" s="75" t="inlineStr">
         <is>
-          <t>T-260316-2</t>
+          <t>T-260316-1</t>
         </is>
       </c>
       <c r="D66" s="76" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="C67" s="66" t="inlineStr">
         <is>
-          <t>T-260318-4</t>
+          <t>T-260318-3</t>
         </is>
       </c>
       <c r="D67" s="67" t="inlineStr">
@@ -32459,7 +32459,7 @@
       </c>
       <c r="C68" s="75" t="inlineStr">
         <is>
-          <t>T-260318-5</t>
+          <t>T-260318-4</t>
         </is>
       </c>
       <c r="D68" s="76" t="inlineStr">
@@ -32552,7 +32552,7 @@
       </c>
       <c r="C69" s="66" t="inlineStr">
         <is>
-          <t>T-260325-6</t>
+          <t>T-260325-5</t>
         </is>
       </c>
       <c r="D69" s="67" t="inlineStr">
@@ -32645,7 +32645,7 @@
       </c>
       <c r="C70" s="75" t="inlineStr">
         <is>
-          <t>T-260327-8</t>
+          <t>T-260327-7</t>
         </is>
       </c>
       <c r="D70" s="76" t="inlineStr">
@@ -32738,7 +32738,7 @@
       </c>
       <c r="C71" s="66" t="inlineStr">
         <is>
-          <t>T-260331-11</t>
+          <t>T-260331-10</t>
         </is>
       </c>
       <c r="D71" s="67" t="inlineStr">
@@ -32831,7 +32831,7 @@
       </c>
       <c r="C72" s="75" t="inlineStr">
         <is>
-          <t>T-260303-3</t>
+          <t>T-260303-2</t>
         </is>
       </c>
       <c r="D72" s="76" t="inlineStr">
@@ -32924,7 +32924,7 @@
       </c>
       <c r="C73" s="66" t="inlineStr">
         <is>
-          <t>T-260310-2</t>
+          <t>T-260310-1</t>
         </is>
       </c>
       <c r="D73" s="67" t="inlineStr">
@@ -34260,7 +34260,7 @@
       </c>
       <c r="C5" s="66" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D5" s="66" t="inlineStr">
@@ -34340,7 +34340,7 @@
       </c>
       <c r="C7" s="66" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D7" s="66" t="inlineStr">
@@ -34420,7 +34420,7 @@
       </c>
       <c r="C9" s="66" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D9" s="66" t="inlineStr">
@@ -34460,7 +34460,7 @@
       </c>
       <c r="C10" s="75" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D10" s="75" t="inlineStr">
@@ -34500,7 +34500,7 @@
       </c>
       <c r="C11" s="66" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D11" s="66" t="inlineStr">
@@ -34540,7 +34540,7 @@
       </c>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D12" s="75" t="inlineStr">
@@ -34580,7 +34580,7 @@
       </c>
       <c r="C13" s="66" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D13" s="66" t="inlineStr">
@@ -34620,7 +34620,7 @@
       </c>
       <c r="C14" s="75" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D14" s="75" t="inlineStr">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D15" s="66" t="inlineStr">
@@ -34700,7 +34700,7 @@
       </c>
       <c r="C16" s="75" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D16" s="75" t="inlineStr">
@@ -34740,7 +34740,7 @@
       </c>
       <c r="C17" s="66" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D17" s="66" t="inlineStr">
@@ -34780,7 +34780,7 @@
       </c>
       <c r="C18" s="75" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D18" s="75" t="inlineStr">
@@ -34820,7 +34820,7 @@
       </c>
       <c r="C19" s="66" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D19" s="66" t="inlineStr">
@@ -34860,7 +34860,7 @@
       </c>
       <c r="C20" s="75" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D20" s="75" t="inlineStr">
@@ -34900,7 +34900,7 @@
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D21" s="66" t="inlineStr">
@@ -34940,7 +34940,7 @@
       </c>
       <c r="C22" s="75" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D22" s="75" t="inlineStr">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D23" s="66" t="inlineStr">
@@ -35020,7 +35020,7 @@
       </c>
       <c r="C24" s="75" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D24" s="75" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="C25" s="66" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D25" s="66" t="inlineStr">
@@ -35100,7 +35100,7 @@
       </c>
       <c r="C26" s="75" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D26" s="75" t="inlineStr">
@@ -35140,7 +35140,7 @@
       </c>
       <c r="C27" s="66" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D27" s="66" t="inlineStr">
@@ -35260,7 +35260,7 @@
       </c>
       <c r="C30" s="75" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D30" s="75" t="inlineStr">
@@ -35300,7 +35300,7 @@
       </c>
       <c r="C31" s="66" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D31" s="66" t="inlineStr">
@@ -35340,7 +35340,7 @@
       </c>
       <c r="C32" s="75" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D32" s="75" t="inlineStr">
@@ -35380,7 +35380,7 @@
       </c>
       <c r="C33" s="66" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D33" s="66" t="inlineStr">
@@ -35420,7 +35420,7 @@
       </c>
       <c r="C34" s="75" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D34" s="75" t="inlineStr">
@@ -35460,7 +35460,7 @@
       </c>
       <c r="C35" s="66" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D35" s="66" t="inlineStr">
@@ -35540,7 +35540,7 @@
       </c>
       <c r="C37" s="66" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D37" s="66" t="inlineStr">
@@ -35580,7 +35580,7 @@
       </c>
       <c r="C38" s="75" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D38" s="75" t="inlineStr">
@@ -35620,7 +35620,7 @@
       </c>
       <c r="C39" s="66" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D39" s="66" t="inlineStr">
@@ -35740,7 +35740,7 @@
       </c>
       <c r="C42" s="75" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D42" s="75" t="inlineStr">
@@ -35780,7 +35780,7 @@
       </c>
       <c r="C43" s="66" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D43" s="66" t="inlineStr">
@@ -35820,7 +35820,7 @@
       </c>
       <c r="C44" s="75" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D44" s="75" t="inlineStr">
@@ -35860,7 +35860,7 @@
       </c>
       <c r="C45" s="66" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D45" s="66" t="inlineStr">
@@ -35900,7 +35900,7 @@
       </c>
       <c r="C46" s="75" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D46" s="75" t="inlineStr">
@@ -35940,7 +35940,7 @@
       </c>
       <c r="C47" s="66" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D47" s="66" t="inlineStr">
@@ -36020,7 +36020,7 @@
       </c>
       <c r="C49" s="66" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D49" s="66" t="inlineStr">
@@ -36060,7 +36060,7 @@
       </c>
       <c r="C50" s="75" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D50" s="75" t="inlineStr">
@@ -36100,7 +36100,7 @@
       </c>
       <c r="C51" s="66" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D51" s="66" t="inlineStr">
@@ -36140,7 +36140,7 @@
       </c>
       <c r="C52" s="75" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D52" s="75" t="inlineStr">
@@ -36180,7 +36180,7 @@
       </c>
       <c r="C53" s="66" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D53" s="66" t="inlineStr">
@@ -36220,7 +36220,7 @@
       </c>
       <c r="C54" s="75" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D54" s="75" t="inlineStr">
@@ -36260,7 +36260,7 @@
       </c>
       <c r="C55" s="66" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D55" s="66" t="inlineStr">
@@ -36300,7 +36300,7 @@
       </c>
       <c r="C56" s="75" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D56" s="75" t="inlineStr">
@@ -36340,7 +36340,7 @@
       </c>
       <c r="C57" s="66" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D57" s="66" t="inlineStr">
@@ -36380,7 +36380,7 @@
       </c>
       <c r="C58" s="75" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D58" s="75" t="inlineStr">
@@ -36420,7 +36420,7 @@
       </c>
       <c r="C59" s="66" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D59" s="66" t="inlineStr">
@@ -36500,7 +36500,7 @@
       </c>
       <c r="C61" s="66" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D61" s="66" t="inlineStr">
@@ -36540,7 +36540,7 @@
       </c>
       <c r="C62" s="75" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D62" s="75" t="inlineStr">
@@ -36580,7 +36580,7 @@
       </c>
       <c r="C63" s="66" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D63" s="66" t="inlineStr">
@@ -36620,7 +36620,7 @@
       </c>
       <c r="C64" s="75" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D64" s="75" t="inlineStr">
@@ -36700,7 +36700,7 @@
       </c>
       <c r="C66" s="75" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D66" s="75" t="inlineStr">
@@ -36740,7 +36740,7 @@
       </c>
       <c r="C67" s="66" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D67" s="66" t="inlineStr">
@@ -36780,7 +36780,7 @@
       </c>
       <c r="C68" s="75" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D68" s="75" t="inlineStr">
@@ -36820,7 +36820,7 @@
       </c>
       <c r="C69" s="66" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D69" s="66" t="inlineStr">
@@ -36860,7 +36860,7 @@
       </c>
       <c r="C70" s="75" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D70" s="75" t="inlineStr">
@@ -36900,7 +36900,7 @@
       </c>
       <c r="C71" s="66" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D71" s="66" t="inlineStr">
@@ -36940,7 +36940,7 @@
       </c>
       <c r="C72" s="75" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D72" s="75" t="inlineStr">
@@ -36980,7 +36980,7 @@
       </c>
       <c r="C73" s="66" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D73" s="66" t="inlineStr">
@@ -37020,7 +37020,7 @@
       </c>
       <c r="C74" s="75" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D74" s="75" t="inlineStr">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="C76" s="75" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D76" s="75" t="inlineStr">
@@ -37140,7 +37140,7 @@
       </c>
       <c r="C77" s="66" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D77" s="66" t="inlineStr">
@@ -37180,7 +37180,7 @@
       </c>
       <c r="C78" s="75" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D78" s="75" t="inlineStr">
@@ -37220,7 +37220,7 @@
       </c>
       <c r="C79" s="66" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D79" s="66" t="inlineStr">
@@ -37260,7 +37260,7 @@
       </c>
       <c r="C80" s="75" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D80" s="75" t="inlineStr">
@@ -37300,7 +37300,7 @@
       </c>
       <c r="C81" s="66" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D81" s="66" t="inlineStr">
@@ -37340,7 +37340,7 @@
       </c>
       <c r="C82" s="75" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D82" s="75" t="inlineStr">
@@ -37380,7 +37380,7 @@
       </c>
       <c r="C83" s="66" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D83" s="66" t="inlineStr">
@@ -37500,7 +37500,7 @@
       </c>
       <c r="C86" s="75" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D86" s="75" t="inlineStr">
@@ -37540,7 +37540,7 @@
       </c>
       <c r="C87" s="66" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D87" s="66" t="inlineStr">
@@ -37580,7 +37580,7 @@
       </c>
       <c r="C88" s="75" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D88" s="75" t="inlineStr">
@@ -37620,7 +37620,7 @@
       </c>
       <c r="C89" s="66" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D89" s="66" t="inlineStr">
@@ -37660,7 +37660,7 @@
       </c>
       <c r="C90" s="75" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D90" s="75" t="inlineStr">
@@ -37740,7 +37740,7 @@
       </c>
       <c r="C92" s="75" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D92" s="75" t="inlineStr">
@@ -37780,7 +37780,7 @@
       </c>
       <c r="C93" s="66" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D93" s="66" t="inlineStr">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="C94" s="75" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D94" s="75" t="inlineStr">
@@ -37860,7 +37860,7 @@
       </c>
       <c r="C95" s="66" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D95" s="66" t="inlineStr">
@@ -37900,7 +37900,7 @@
       </c>
       <c r="C96" s="75" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D96" s="75" t="inlineStr">
@@ -37940,7 +37940,7 @@
       </c>
       <c r="C97" s="66" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D97" s="66" t="inlineStr">
@@ -37980,7 +37980,7 @@
       </c>
       <c r="C98" s="75" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D98" s="75" t="inlineStr">
@@ -38020,7 +38020,7 @@
       </c>
       <c r="C99" s="66" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="66" t="inlineStr">
@@ -38100,7 +38100,7 @@
       </c>
       <c r="C101" s="66" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D101" s="66" t="inlineStr">
@@ -38140,7 +38140,7 @@
       </c>
       <c r="C102" s="75" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D102" s="75" t="inlineStr">
@@ -38180,7 +38180,7 @@
       </c>
       <c r="C103" s="66" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D103" s="66" t="inlineStr">
@@ -38220,7 +38220,7 @@
       </c>
       <c r="C104" s="75" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D104" s="75" t="inlineStr">
@@ -38260,7 +38260,7 @@
       </c>
       <c r="C105" s="66" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D105" s="66" t="inlineStr">
@@ -38300,7 +38300,7 @@
       </c>
       <c r="C106" s="75" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D106" s="75" t="inlineStr">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C108" s="75" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D108" s="75" t="inlineStr">
@@ -38456,7 +38456,7 @@
       </c>
       <c r="C110" s="75" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D110" s="75" t="inlineStr">
@@ -38532,7 +38532,7 @@
       </c>
       <c r="C112" s="75" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D112" s="75" t="inlineStr">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C113" s="66" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D113" s="66" t="inlineStr">
@@ -38612,7 +38612,7 @@
       </c>
       <c r="C114" s="75" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D114" s="75" t="inlineStr">
@@ -38652,7 +38652,7 @@
       </c>
       <c r="C115" s="66" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D115" s="66" t="inlineStr">
@@ -38732,7 +38732,7 @@
       </c>
       <c r="C117" s="66" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D117" s="66" t="inlineStr">
@@ -38772,7 +38772,7 @@
       </c>
       <c r="C118" s="75" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D118" s="75" t="inlineStr">
@@ -38812,7 +38812,7 @@
       </c>
       <c r="C119" s="66" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D119" s="66" t="inlineStr">
@@ -38852,7 +38852,7 @@
       </c>
       <c r="C120" s="75" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D120" s="75" t="inlineStr">
@@ -38892,7 +38892,7 @@
       </c>
       <c r="C121" s="66" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D121" s="66" t="inlineStr">
@@ -38972,7 +38972,7 @@
       </c>
       <c r="C123" s="66" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D123" s="66" t="inlineStr">
@@ -39012,7 +39012,7 @@
       </c>
       <c r="C124" s="75" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D124" s="75" t="inlineStr">
@@ -39052,7 +39052,7 @@
       </c>
       <c r="C125" s="66" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D125" s="66" t="inlineStr">
@@ -39092,7 +39092,7 @@
       </c>
       <c r="C126" s="75" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D126" s="75" t="inlineStr">
@@ -39132,7 +39132,7 @@
       </c>
       <c r="C127" s="66" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D127" s="66" t="inlineStr">
@@ -39172,7 +39172,7 @@
       </c>
       <c r="C128" s="75" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D128" s="75" t="inlineStr">
@@ -39212,7 +39212,7 @@
       </c>
       <c r="C129" s="66" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D129" s="66" t="inlineStr">
@@ -39252,7 +39252,7 @@
       </c>
       <c r="C130" s="75" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D130" s="75" t="inlineStr">
@@ -39292,7 +39292,7 @@
       </c>
       <c r="C131" s="66" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D131" s="66" t="inlineStr">
@@ -39332,7 +39332,7 @@
       </c>
       <c r="C132" s="75" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D132" s="75" t="inlineStr">
@@ -39372,7 +39372,7 @@
       </c>
       <c r="C133" s="66" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D133" s="66" t="inlineStr">
@@ -39412,7 +39412,7 @@
       </c>
       <c r="C134" s="75" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D134" s="75" t="inlineStr">
@@ -39452,7 +39452,7 @@
       </c>
       <c r="C135" s="66" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D135" s="66" t="inlineStr">
@@ -39492,7 +39492,7 @@
       </c>
       <c r="C136" s="75" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D136" s="75" t="inlineStr">
@@ -39532,7 +39532,7 @@
       </c>
       <c r="C137" s="66" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D137" s="66" t="inlineStr">
@@ -39572,7 +39572,7 @@
       </c>
       <c r="C138" s="75" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D138" s="75" t="inlineStr">
@@ -39612,7 +39612,7 @@
       </c>
       <c r="C139" s="66" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D139" s="66" t="inlineStr">
@@ -39652,7 +39652,7 @@
       </c>
       <c r="C140" s="75" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D140" s="75" t="inlineStr">
@@ -39692,7 +39692,7 @@
       </c>
       <c r="C141" s="66" t="inlineStr">
         <is>
-          <t>T-260331-8</t>
+          <t>T-260331-7</t>
         </is>
       </c>
       <c r="D141" s="66" t="inlineStr">
@@ -39732,7 +39732,7 @@
       </c>
       <c r="C142" s="75" t="inlineStr">
         <is>
-          <t>T-260331-9</t>
+          <t>T-260331-8</t>
         </is>
       </c>
       <c r="D142" s="75" t="inlineStr">
@@ -39772,7 +39772,7 @@
       </c>
       <c r="C143" s="66" t="inlineStr">
         <is>
-          <t>T-260331-10</t>
+          <t>T-260331-9</t>
         </is>
       </c>
       <c r="D143" s="66" t="inlineStr">
@@ -39812,7 +39812,7 @@
       </c>
       <c r="C144" s="75" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D144" s="75" t="inlineStr">
@@ -39852,7 +39852,7 @@
       </c>
       <c r="C145" s="66" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D145" s="66" t="inlineStr">
@@ -39892,7 +39892,7 @@
       </c>
       <c r="C146" s="75" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D146" s="75" t="inlineStr">
@@ -39932,7 +39932,7 @@
       </c>
       <c r="C147" s="66" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D147" s="66" t="inlineStr">
@@ -39972,7 +39972,7 @@
       </c>
       <c r="C148" s="75" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D148" s="75" t="inlineStr">
@@ -40012,7 +40012,7 @@
       </c>
       <c r="C149" s="66" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D149" s="66" t="inlineStr">
@@ -40052,7 +40052,7 @@
       </c>
       <c r="C150" s="75" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D150" s="75" t="inlineStr">
@@ -40092,7 +40092,7 @@
       </c>
       <c r="C151" s="66" t="inlineStr">
         <is>
-          <t>T-260318-3</t>
+          <t>T-260318-2</t>
         </is>
       </c>
       <c r="D151" s="66" t="inlineStr">
@@ -40132,7 +40132,7 @@
       </c>
       <c r="C152" s="75" t="inlineStr">
         <is>
-          <t>T-260325-4</t>
+          <t>T-260325-3</t>
         </is>
       </c>
       <c r="D152" s="75" t="inlineStr">
@@ -40172,7 +40172,7 @@
       </c>
       <c r="C153" s="66" t="inlineStr">
         <is>
-          <t>T-260325-5</t>
+          <t>T-260325-4</t>
         </is>
       </c>
       <c r="D153" s="66" t="inlineStr">
@@ -40212,7 +40212,7 @@
       </c>
       <c r="C154" s="75" t="inlineStr">
         <is>
-          <t>T-260316-2</t>
+          <t>T-260316-1</t>
         </is>
       </c>
       <c r="D154" s="75" t="inlineStr">
@@ -40252,7 +40252,7 @@
       </c>
       <c r="C155" s="66" t="inlineStr">
         <is>
-          <t>T-260318-4</t>
+          <t>T-260318-3</t>
         </is>
       </c>
       <c r="D155" s="66" t="inlineStr">
@@ -40292,7 +40292,7 @@
       </c>
       <c r="C156" s="75" t="inlineStr">
         <is>
-          <t>T-260318-5</t>
+          <t>T-260318-4</t>
         </is>
       </c>
       <c r="D156" s="75" t="inlineStr">
@@ -40332,7 +40332,7 @@
       </c>
       <c r="C157" s="66" t="inlineStr">
         <is>
-          <t>T-260325-6</t>
+          <t>T-260325-5</t>
         </is>
       </c>
       <c r="D157" s="66" t="inlineStr">
@@ -40372,7 +40372,7 @@
       </c>
       <c r="C158" s="75" t="inlineStr">
         <is>
-          <t>T-260327-8</t>
+          <t>T-260327-7</t>
         </is>
       </c>
       <c r="D158" s="75" t="inlineStr">
@@ -40412,7 +40412,7 @@
       </c>
       <c r="C159" s="66" t="inlineStr">
         <is>
-          <t>T-260331-11</t>
+          <t>T-260331-10</t>
         </is>
       </c>
       <c r="D159" s="66" t="inlineStr">
@@ -40452,7 +40452,7 @@
       </c>
       <c r="C160" s="75" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D160" s="75" t="inlineStr">
@@ -40492,7 +40492,7 @@
       </c>
       <c r="C161" s="66" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D161" s="66" t="inlineStr">
@@ -40532,7 +40532,7 @@
       </c>
       <c r="C162" s="75" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D162" s="75" t="inlineStr">
@@ -40572,7 +40572,7 @@
       </c>
       <c r="C163" s="66" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D163" s="66" t="inlineStr">
@@ -40612,7 +40612,7 @@
       </c>
       <c r="C164" s="75" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D164" s="75" t="inlineStr">
@@ -40652,7 +40652,7 @@
       </c>
       <c r="C165" s="66" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D165" s="66" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="C166" s="75" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D166" s="75" t="inlineStr">
@@ -40732,7 +40732,7 @@
       </c>
       <c r="C167" s="66" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D167" s="66" t="inlineStr">
@@ -40812,7 +40812,7 @@
       </c>
       <c r="C169" s="66" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D169" s="66" t="inlineStr">
@@ -40852,7 +40852,7 @@
       </c>
       <c r="C170" s="75" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D170" s="75" t="inlineStr">
@@ -40892,7 +40892,7 @@
       </c>
       <c r="C171" s="66" t="inlineStr">
         <is>
-          <t>T-260303-3</t>
+          <t>T-260303-2</t>
         </is>
       </c>
       <c r="D171" s="66" t="inlineStr">
@@ -40932,7 +40932,7 @@
       </c>
       <c r="C172" s="75" t="inlineStr">
         <is>
-          <t>T-260310-2</t>
+          <t>T-260310-1</t>
         </is>
       </c>
       <c r="D172" s="75" t="inlineStr">
@@ -40972,7 +40972,7 @@
       </c>
       <c r="C173" s="66" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D173" s="66" t="inlineStr">
@@ -41012,7 +41012,7 @@
       </c>
       <c r="C174" s="75" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D174" s="75" t="inlineStr">
@@ -41052,7 +41052,7 @@
       </c>
       <c r="C175" s="66" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D175" s="66" t="inlineStr">
@@ -41092,7 +41092,7 @@
       </c>
       <c r="C176" s="75" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D176" s="75" t="inlineStr">
@@ -41132,7 +41132,7 @@
       </c>
       <c r="C177" s="66" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D177" s="66" t="inlineStr">
@@ -41606,7 +41606,7 @@
       </c>
       <c r="C5" s="66" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D5" s="66" t="inlineStr">
@@ -41641,7 +41641,7 @@
       </c>
       <c r="C6" s="75" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D6" s="75" t="inlineStr">
@@ -41676,7 +41676,7 @@
       </c>
       <c r="C7" s="66" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D7" s="66" t="inlineStr">
@@ -41711,7 +41711,7 @@
       </c>
       <c r="C8" s="75" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D8" s="75" t="inlineStr">
@@ -41746,7 +41746,7 @@
       </c>
       <c r="C9" s="66" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D9" s="66" t="inlineStr">
@@ -41851,7 +41851,7 @@
       </c>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D12" s="75" t="inlineStr">
@@ -41886,7 +41886,7 @@
       </c>
       <c r="C13" s="66" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D13" s="66" t="inlineStr">
@@ -41921,7 +41921,7 @@
       </c>
       <c r="C14" s="75" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D14" s="75" t="inlineStr">
@@ -41956,7 +41956,7 @@
       </c>
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D15" s="66" t="inlineStr">
@@ -41991,7 +41991,7 @@
       </c>
       <c r="C16" s="75" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D16" s="75" t="inlineStr">
@@ -42096,7 +42096,7 @@
       </c>
       <c r="C19" s="66" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D19" s="66" t="inlineStr">
@@ -42131,7 +42131,7 @@
       </c>
       <c r="C20" s="75" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D20" s="75" t="inlineStr">
@@ -42166,7 +42166,7 @@
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D21" s="66" t="inlineStr">
@@ -42201,7 +42201,7 @@
       </c>
       <c r="C22" s="75" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D22" s="75" t="inlineStr">
@@ -42236,7 +42236,7 @@
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D23" s="66" t="inlineStr">
@@ -42271,7 +42271,7 @@
       </c>
       <c r="C24" s="75" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D24" s="75" t="inlineStr">
@@ -42306,7 +42306,7 @@
       </c>
       <c r="C25" s="66" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D25" s="66" t="inlineStr">
@@ -42341,7 +42341,7 @@
       </c>
       <c r="C26" s="75" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D26" s="75" t="inlineStr">
@@ -42411,7 +42411,7 @@
       </c>
       <c r="C28" s="75" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D28" s="75" t="inlineStr">
@@ -42481,7 +42481,7 @@
       </c>
       <c r="C30" s="75" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D30" s="75" t="inlineStr">
@@ -42516,7 +42516,7 @@
       </c>
       <c r="C31" s="66" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D31" s="66" t="inlineStr">
@@ -42551,7 +42551,7 @@
       </c>
       <c r="C32" s="75" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D32" s="75" t="inlineStr">
@@ -42586,7 +42586,7 @@
       </c>
       <c r="C33" s="66" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D33" s="66" t="inlineStr">
@@ -42621,7 +42621,7 @@
       </c>
       <c r="C34" s="75" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D34" s="75" t="inlineStr">
@@ -42656,7 +42656,7 @@
       </c>
       <c r="C35" s="66" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D35" s="66" t="inlineStr">
@@ -42691,7 +42691,7 @@
       </c>
       <c r="C36" s="75" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D36" s="75" t="inlineStr">
@@ -42726,7 +42726,7 @@
       </c>
       <c r="C37" s="66" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D37" s="66" t="inlineStr">
@@ -42761,7 +42761,7 @@
       </c>
       <c r="C38" s="75" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D38" s="75" t="inlineStr">
@@ -42796,7 +42796,7 @@
       </c>
       <c r="C39" s="66" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D39" s="66" t="inlineStr">
@@ -42831,7 +42831,7 @@
       </c>
       <c r="C40" s="75" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D40" s="75" t="inlineStr">
@@ -42866,7 +42866,7 @@
       </c>
       <c r="C41" s="66" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D41" s="66" t="inlineStr">
@@ -42901,7 +42901,7 @@
       </c>
       <c r="C42" s="75" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D42" s="75" t="inlineStr">
@@ -42936,7 +42936,7 @@
       </c>
       <c r="C43" s="66" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D43" s="66" t="inlineStr">
@@ -42971,7 +42971,7 @@
       </c>
       <c r="C44" s="75" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D44" s="75" t="inlineStr">
@@ -43006,7 +43006,7 @@
       </c>
       <c r="C45" s="66" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D45" s="66" t="inlineStr">
@@ -43041,7 +43041,7 @@
       </c>
       <c r="C46" s="75" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D46" s="75" t="inlineStr">
@@ -43076,7 +43076,7 @@
       </c>
       <c r="C47" s="66" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D47" s="66" t="inlineStr">
@@ -43111,7 +43111,7 @@
       </c>
       <c r="C48" s="75" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D48" s="75" t="inlineStr">
@@ -43146,7 +43146,7 @@
       </c>
       <c r="C49" s="66" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D49" s="66" t="inlineStr">
@@ -43181,7 +43181,7 @@
       </c>
       <c r="C50" s="75" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D50" s="75" t="inlineStr">
@@ -43216,7 +43216,7 @@
       </c>
       <c r="C51" s="66" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D51" s="66" t="inlineStr">
@@ -43251,7 +43251,7 @@
       </c>
       <c r="C52" s="75" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D52" s="75" t="inlineStr">
@@ -43321,7 +43321,7 @@
       </c>
       <c r="C54" s="75" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D54" s="75" t="inlineStr">
@@ -43356,7 +43356,7 @@
       </c>
       <c r="C55" s="66" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D55" s="66" t="inlineStr">
@@ -43391,7 +43391,7 @@
       </c>
       <c r="C56" s="75" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D56" s="75" t="inlineStr">
@@ -43426,7 +43426,7 @@
       </c>
       <c r="C57" s="66" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D57" s="66" t="inlineStr">
@@ -43461,7 +43461,7 @@
       </c>
       <c r="C58" s="75" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D58" s="75" t="inlineStr">
@@ -43566,7 +43566,7 @@
       </c>
       <c r="C61" s="66" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D61" s="66" t="inlineStr">
@@ -43636,7 +43636,7 @@
       </c>
       <c r="C63" s="66" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D63" s="66" t="inlineStr">
@@ -43706,7 +43706,7 @@
       </c>
       <c r="C65" s="66" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D65" s="66" t="inlineStr">
@@ -43741,7 +43741,7 @@
       </c>
       <c r="C66" s="75" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D66" s="75" t="inlineStr">
@@ -43811,7 +43811,7 @@
       </c>
       <c r="C68" s="75" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D68" s="75" t="inlineStr">
@@ -43846,7 +43846,7 @@
       </c>
       <c r="C69" s="66" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D69" s="66" t="inlineStr">
@@ -43881,7 +43881,7 @@
       </c>
       <c r="C70" s="75" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D70" s="75" t="inlineStr">
@@ -43916,7 +43916,7 @@
       </c>
       <c r="C71" s="66" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D71" s="66" t="inlineStr">
@@ -43951,7 +43951,7 @@
       </c>
       <c r="C72" s="75" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D72" s="75" t="inlineStr">
@@ -43986,7 +43986,7 @@
       </c>
       <c r="C73" s="66" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D73" s="66" t="inlineStr">
@@ -44056,7 +44056,7 @@
       </c>
       <c r="C75" s="66" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D75" s="66" t="inlineStr">
@@ -44091,7 +44091,7 @@
       </c>
       <c r="C76" s="75" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D76" s="75" t="inlineStr">
@@ -44126,7 +44126,7 @@
       </c>
       <c r="C77" s="66" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D77" s="66" t="inlineStr">
@@ -44161,7 +44161,7 @@
       </c>
       <c r="C78" s="75" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D78" s="75" t="inlineStr">
@@ -44196,7 +44196,7 @@
       </c>
       <c r="C79" s="66" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D79" s="66" t="inlineStr">
@@ -44266,7 +44266,7 @@
       </c>
       <c r="C81" s="66" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D81" s="66" t="inlineStr">
@@ -44301,7 +44301,7 @@
       </c>
       <c r="C82" s="75" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D82" s="75" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="C83" s="66" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D83" s="66" t="inlineStr">
@@ -44371,7 +44371,7 @@
       </c>
       <c r="C84" s="75" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D84" s="75" t="inlineStr">
@@ -44406,7 +44406,7 @@
       </c>
       <c r="C85" s="66" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D85" s="66" t="inlineStr">
@@ -44441,7 +44441,7 @@
       </c>
       <c r="C86" s="75" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D86" s="75" t="inlineStr">
@@ -44476,7 +44476,7 @@
       </c>
       <c r="C87" s="66" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D87" s="66" t="inlineStr">
@@ -44511,7 +44511,7 @@
       </c>
       <c r="C88" s="75" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D88" s="75" t="inlineStr">
@@ -44546,7 +44546,7 @@
       </c>
       <c r="C89" s="66" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D89" s="66" t="inlineStr">
@@ -44581,7 +44581,7 @@
       </c>
       <c r="C90" s="75" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D90" s="75" t="inlineStr">
@@ -44651,7 +44651,7 @@
       </c>
       <c r="C92" s="75" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D92" s="75" t="inlineStr">
@@ -44686,7 +44686,7 @@
       </c>
       <c r="C93" s="66" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D93" s="66" t="inlineStr">
@@ -44721,7 +44721,7 @@
       </c>
       <c r="C94" s="75" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D94" s="75" t="inlineStr">
@@ -44756,7 +44756,7 @@
       </c>
       <c r="C95" s="66" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D95" s="66" t="inlineStr">
@@ -44791,7 +44791,7 @@
       </c>
       <c r="C96" s="75" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D96" s="75" t="inlineStr">
@@ -44826,7 +44826,7 @@
       </c>
       <c r="C97" s="66" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D97" s="66" t="inlineStr">
@@ -44896,7 +44896,7 @@
       </c>
       <c r="C99" s="66" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="66" t="inlineStr">
@@ -44931,7 +44931,7 @@
       </c>
       <c r="C100" s="75" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D100" s="75" t="inlineStr">
@@ -44966,7 +44966,7 @@
       </c>
       <c r="C101" s="66" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D101" s="66" t="inlineStr">
@@ -45001,7 +45001,7 @@
       </c>
       <c r="C102" s="75" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D102" s="75" t="inlineStr">
@@ -45036,7 +45036,7 @@
       </c>
       <c r="C103" s="66" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D103" s="66" t="inlineStr">
@@ -45071,7 +45071,7 @@
       </c>
       <c r="C104" s="75" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D104" s="75" t="inlineStr">
@@ -45106,7 +45106,7 @@
       </c>
       <c r="C105" s="66" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D105" s="66" t="inlineStr">
@@ -45141,7 +45141,7 @@
       </c>
       <c r="C106" s="75" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D106" s="75" t="inlineStr">
@@ -45211,7 +45211,7 @@
       </c>
       <c r="C108" s="75" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D108" s="75" t="inlineStr">
@@ -45246,7 +45246,7 @@
       </c>
       <c r="C109" s="66" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D109" s="66" t="inlineStr">
@@ -45281,7 +45281,7 @@
       </c>
       <c r="C110" s="75" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D110" s="75" t="inlineStr">
@@ -46305,7 +46305,7 @@
       </c>
       <c r="B5" s="66" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="C5" s="66" t="inlineStr">
@@ -46395,7 +46395,7 @@
       </c>
       <c r="B8" s="75" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="C8" s="75" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="B9" s="66" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="C9" s="66" t="inlineStr">
@@ -46485,7 +46485,7 @@
       </c>
       <c r="B11" s="66" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="C11" s="66" t="inlineStr">
@@ -46515,7 +46515,7 @@
       </c>
       <c r="B12" s="75" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="C12" s="75" t="inlineStr">
@@ -46575,7 +46575,7 @@
       </c>
       <c r="B14" s="75" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="C14" s="75" t="inlineStr">
@@ -46605,7 +46605,7 @@
       </c>
       <c r="B15" s="66" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="C15" s="66" t="inlineStr">
@@ -46635,7 +46635,7 @@
       </c>
       <c r="B16" s="75" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="C16" s="75" t="inlineStr">
@@ -46665,7 +46665,7 @@
       </c>
       <c r="B17" s="66" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="C17" s="66" t="inlineStr">
@@ -46695,7 +46695,7 @@
       </c>
       <c r="B18" s="75" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="C18" s="75" t="inlineStr">
@@ -46725,7 +46725,7 @@
       </c>
       <c r="B19" s="66" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="C19" s="66" t="inlineStr">
@@ -46755,7 +46755,7 @@
       </c>
       <c r="B20" s="75" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="C20" s="75" t="inlineStr">
@@ -46785,7 +46785,7 @@
       </c>
       <c r="B21" s="66" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="C21" s="66" t="inlineStr">
@@ -46815,7 +46815,7 @@
       </c>
       <c r="B22" s="75" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="C22" s="75" t="inlineStr">
@@ -46845,7 +46845,7 @@
       </c>
       <c r="B23" s="66" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="C23" s="66" t="inlineStr">
@@ -46875,7 +46875,7 @@
       </c>
       <c r="B24" s="75" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="C24" s="75" t="inlineStr">
@@ -46905,7 +46905,7 @@
       </c>
       <c r="B25" s="66" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="C25" s="66" t="inlineStr">
@@ -46935,7 +46935,7 @@
       </c>
       <c r="B26" s="75" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="C26" s="75" t="inlineStr">
@@ -46965,7 +46965,7 @@
       </c>
       <c r="B27" s="66" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="C27" s="66" t="inlineStr">
@@ -46995,7 +46995,7 @@
       </c>
       <c r="B28" s="75" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="C28" s="75" t="inlineStr">
@@ -47025,7 +47025,7 @@
       </c>
       <c r="B29" s="66" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="C29" s="66" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="B30" s="75" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="C30" s="75" t="inlineStr">
@@ -47085,7 +47085,7 @@
       </c>
       <c r="B31" s="66" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="C31" s="66" t="inlineStr">
@@ -47115,7 +47115,7 @@
       </c>
       <c r="B32" s="75" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="C32" s="75" t="inlineStr">
@@ -47145,7 +47145,7 @@
       </c>
       <c r="B33" s="66" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="C33" s="66" t="inlineStr">
@@ -47205,7 +47205,7 @@
       </c>
       <c r="B35" s="66" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="C35" s="66" t="inlineStr">
@@ -47235,7 +47235,7 @@
       </c>
       <c r="B36" s="75" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="C36" s="75" t="inlineStr">
@@ -47265,7 +47265,7 @@
       </c>
       <c r="B37" s="66" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="C37" s="66" t="inlineStr">
@@ -47325,7 +47325,7 @@
       </c>
       <c r="B39" s="66" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="C39" s="66" t="inlineStr">
@@ -47355,7 +47355,7 @@
       </c>
       <c r="B40" s="75" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="C40" s="75" t="inlineStr">
@@ -47385,7 +47385,7 @@
       </c>
       <c r="B41" s="66" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="C41" s="66" t="inlineStr">
@@ -47415,7 +47415,7 @@
       </c>
       <c r="B42" s="75" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="C42" s="75" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B43" s="66" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="C43" s="66" t="inlineStr">
@@ -47475,7 +47475,7 @@
       </c>
       <c r="B44" s="75" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="C44" s="75" t="inlineStr">
@@ -47505,7 +47505,7 @@
       </c>
       <c r="B45" s="66" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="C45" s="66" t="inlineStr">
@@ -47535,7 +47535,7 @@
       </c>
       <c r="B46" s="75" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="C46" s="75" t="inlineStr">
@@ -47565,7 +47565,7 @@
       </c>
       <c r="B47" s="66" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="C47" s="66" t="inlineStr">
@@ -47595,7 +47595,7 @@
       </c>
       <c r="B48" s="75" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="C48" s="75" t="inlineStr">
@@ -47655,7 +47655,7 @@
       </c>
       <c r="B50" s="75" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="C50" s="75" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="B51" s="66" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="C51" s="66" t="inlineStr">
@@ -47715,7 +47715,7 @@
       </c>
       <c r="B52" s="75" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="C52" s="75" t="inlineStr">
@@ -47745,7 +47745,7 @@
       </c>
       <c r="B53" s="66" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="C53" s="66" t="inlineStr">
@@ -47775,7 +47775,7 @@
       </c>
       <c r="B54" s="75" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="C54" s="75" t="inlineStr">
@@ -47805,7 +47805,7 @@
       </c>
       <c r="B55" s="66" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="C55" s="66" t="inlineStr">
@@ -47835,7 +47835,7 @@
       </c>
       <c r="B56" s="75" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="C56" s="75" t="inlineStr">
@@ -47865,7 +47865,7 @@
       </c>
       <c r="B57" s="66" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="C57" s="66" t="inlineStr">
@@ -47895,7 +47895,7 @@
       </c>
       <c r="B58" s="75" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="C58" s="75" t="inlineStr">
@@ -47955,7 +47955,7 @@
       </c>
       <c r="B60" s="75" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="C60" s="75" t="inlineStr">
@@ -47985,7 +47985,7 @@
       </c>
       <c r="B61" s="66" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="C61" s="66" t="inlineStr">
@@ -48015,7 +48015,7 @@
       </c>
       <c r="B62" s="75" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="C62" s="75" t="inlineStr">
@@ -48045,7 +48045,7 @@
       </c>
       <c r="B63" s="66" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="C63" s="66" t="inlineStr">
@@ -48075,7 +48075,7 @@
       </c>
       <c r="B64" s="75" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="C64" s="75" t="inlineStr">
@@ -48105,7 +48105,7 @@
       </c>
       <c r="B65" s="66" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="C65" s="66" t="inlineStr">
@@ -48135,7 +48135,7 @@
       </c>
       <c r="B66" s="75" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="C66" s="75" t="inlineStr">
@@ -48165,7 +48165,7 @@
       </c>
       <c r="B67" s="66" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="C67" s="66" t="inlineStr">
@@ -48195,7 +48195,7 @@
       </c>
       <c r="B68" s="75" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="C68" s="75" t="inlineStr">
@@ -48225,7 +48225,7 @@
       </c>
       <c r="B69" s="66" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="C69" s="66" t="inlineStr">
@@ -48255,7 +48255,7 @@
       </c>
       <c r="B70" s="75" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="C70" s="75" t="inlineStr">
@@ -48285,7 +48285,7 @@
       </c>
       <c r="B71" s="66" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="C71" s="66" t="inlineStr">
@@ -48315,7 +48315,7 @@
       </c>
       <c r="B72" s="75" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="C72" s="75" t="inlineStr">
@@ -48345,7 +48345,7 @@
       </c>
       <c r="B73" s="66" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="C73" s="66" t="inlineStr">
@@ -48375,7 +48375,7 @@
       </c>
       <c r="B74" s="75" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="C74" s="75" t="inlineStr">
@@ -48405,7 +48405,7 @@
       </c>
       <c r="B75" s="66" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="C75" s="66" t="inlineStr">
@@ -48435,7 +48435,7 @@
       </c>
       <c r="B76" s="75" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="C76" s="75" t="inlineStr">
@@ -48465,7 +48465,7 @@
       </c>
       <c r="B77" s="66" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="C77" s="66" t="inlineStr">
@@ -48495,7 +48495,7 @@
       </c>
       <c r="B78" s="75" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="C78" s="75" t="inlineStr">
@@ -48525,7 +48525,7 @@
       </c>
       <c r="B79" s="66" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="C79" s="66" t="inlineStr">
@@ -48585,7 +48585,7 @@
       </c>
       <c r="B81" s="66" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="C81" s="66" t="inlineStr">
@@ -48615,7 +48615,7 @@
       </c>
       <c r="B82" s="75" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="C82" s="75" t="inlineStr">
@@ -48645,7 +48645,7 @@
       </c>
       <c r="B83" s="66" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="C83" s="66" t="inlineStr">
@@ -48675,7 +48675,7 @@
       </c>
       <c r="B84" s="75" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="C84" s="75" t="inlineStr">
@@ -48705,7 +48705,7 @@
       </c>
       <c r="B85" s="66" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="C85" s="66" t="inlineStr">
@@ -48735,7 +48735,7 @@
       </c>
       <c r="B86" s="75" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="C86" s="75" t="inlineStr">
@@ -48765,7 +48765,7 @@
       </c>
       <c r="B87" s="66" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="C87" s="66" t="inlineStr">
@@ -48795,7 +48795,7 @@
       </c>
       <c r="B88" s="75" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="C88" s="75" t="inlineStr">
@@ -48825,7 +48825,7 @@
       </c>
       <c r="B89" s="66" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="C89" s="66" t="inlineStr">
@@ -48855,7 +48855,7 @@
       </c>
       <c r="B90" s="75" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="C90" s="75" t="inlineStr">
@@ -48915,7 +48915,7 @@
       </c>
       <c r="B92" s="75" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="C92" s="75" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="B93" s="66" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="C93" s="66" t="inlineStr">
@@ -48975,7 +48975,7 @@
       </c>
       <c r="B94" s="75" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="C94" s="75" t="inlineStr">
@@ -49005,7 +49005,7 @@
       </c>
       <c r="B95" s="66" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="C95" s="66" t="inlineStr">
@@ -49035,7 +49035,7 @@
       </c>
       <c r="B96" s="75" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="C96" s="75" t="inlineStr">
@@ -49065,7 +49065,7 @@
       </c>
       <c r="B97" s="66" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="C97" s="66" t="inlineStr">
@@ -49095,7 +49095,7 @@
       </c>
       <c r="B98" s="75" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="C98" s="75" t="inlineStr">
@@ -49125,7 +49125,7 @@
       </c>
       <c r="B99" s="66" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="C99" s="66" t="inlineStr">
@@ -49155,7 +49155,7 @@
       </c>
       <c r="B100" s="75" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="C100" s="75" t="inlineStr">
@@ -49305,7 +49305,7 @@
       </c>
       <c r="B105" s="66" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="C105" s="66" t="inlineStr">
@@ -49365,7 +49365,7 @@
       </c>
       <c r="B107" s="66" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="C107" s="66" t="inlineStr">
@@ -49395,7 +49395,7 @@
       </c>
       <c r="B108" s="75" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="C108" s="75" t="inlineStr">
